--- a/accord/data/marques/marques.xlsx
+++ b/accord/data/marques/marques.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lifestyle by Ennismore</t>
+          <t>LIFESTYLE BY ENNISMORE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Midscale</t>
+          <t>MIDSCALE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>ECONOMY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Luxury</t>
+          <t>LUXURY</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Partner-Brands</t>
+          <t>PARTNER-BRANDS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
